--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N67_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N67_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.40860679215796</v>
+        <v>1.691398603725668</v>
       </c>
       <c r="D2" t="n">
-        <v>9.728362575498242</v>
+        <v>1.580858918518464</v>
       </c>
       <c r="E2" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F2" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.73860897444557</v>
+        <v>5.645023958347405</v>
       </c>
       <c r="D3" t="n">
-        <v>34.03774230519068</v>
+        <v>5.531133124593486</v>
       </c>
       <c r="E3" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F3" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.65398113998627</v>
+        <v>6.281271935247769</v>
       </c>
       <c r="D4" t="n">
-        <v>34.41687507600711</v>
+        <v>5.592742199851156</v>
       </c>
       <c r="E4" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F4" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.98749756774461</v>
+        <v>4.2229683547585</v>
       </c>
       <c r="D5" t="n">
-        <v>26.42194943763879</v>
+        <v>4.293566783616304</v>
       </c>
       <c r="E5" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F5" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.4380072311162</v>
+        <v>3.483676175056382</v>
       </c>
       <c r="D6" t="n">
-        <v>21.88796824643392</v>
+        <v>3.556794840045513</v>
       </c>
       <c r="E6" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F6" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.78888902355984</v>
+        <v>3.703194466328473</v>
       </c>
       <c r="D7" t="n">
-        <v>10.51189802081432</v>
+        <v>1.708183428382327</v>
       </c>
       <c r="E7" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F7" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.6730174888572</v>
+        <v>2.384365341939295</v>
       </c>
       <c r="D8" t="n">
-        <v>13.37758954020325</v>
+        <v>2.173858300283029</v>
       </c>
       <c r="E8" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F8" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.78652440466611</v>
+        <v>3.702810215758244</v>
       </c>
       <c r="D9" t="n">
-        <v>19.92332240140193</v>
+        <v>3.237539890227814</v>
       </c>
       <c r="E9" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F9" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.85545262860521</v>
+        <v>5.014011052148346</v>
       </c>
       <c r="D10" t="n">
-        <v>30.05599575602889</v>
+        <v>4.884099310354695</v>
       </c>
       <c r="E10" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F10" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.483110742554921</v>
+        <v>1.053505495665175</v>
       </c>
       <c r="D11" t="n">
-        <v>7.704297420867845</v>
+        <v>1.251948330891025</v>
       </c>
       <c r="E11" t="n">
-        <v>9.780357992764262</v>
+        <v>1.589308173824193</v>
       </c>
       <c r="F11" t="n">
-        <v>9.669045892251141</v>
+        <v>1.57121995749081</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
